--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tranc\Desktop\Models for sharing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8623685-446A-4514-9BD5-BD770FB1B311}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47301FD9-F621-4DEC-8EBB-53B7592FF830}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16920" windowHeight="9435" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="422">
   <si>
     <t>NVIDIA CORP</t>
   </si>
@@ -1210,9 +1210,6 @@
   </si>
   <si>
     <t>https://finance.yahoo.com/quote/ORCL/earnings/ORCL-Q3-2026-earnings_call-529436.html?err=1</t>
-  </si>
-  <si>
-    <t>Yellow cells are editable. Values persist in data/raw/hyperscaler_config.json.</t>
   </si>
   <si>
     <t>2) Hyperscaler Capex TTM ($M)</t>
@@ -1808,8 +1805,12 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1824,10 +1825,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2148,7 +2145,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>2</v>
@@ -4736,7 +4733,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5964,12 +5961,12 @@
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="115" t="s">
+      <c r="A99" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="B99" s="116"/>
-      <c r="C99" s="116"/>
-      <c r="D99" s="116"/>
+      <c r="B99" s="118"/>
+      <c r="C99" s="118"/>
+      <c r="D99" s="118"/>
     </row>
     <row r="100" spans="1:6" ht="15.75">
       <c r="A100" s="7" t="s">
@@ -6004,12 +6001,12 @@
       </c>
     </row>
     <row r="104" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A104" s="126" t="s">
+      <c r="A104" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="B104" s="123"/>
-      <c r="C104" s="123"/>
-      <c r="D104" s="123"/>
+      <c r="B104" s="120"/>
+      <c r="C104" s="120"/>
+      <c r="D104" s="120"/>
     </row>
     <row r="107" spans="1:6" ht="15.75">
       <c r="A107" s="54" t="s">
@@ -6504,15 +6501,15 @@
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="117" t="s">
+      <c r="A37" s="121" t="s">
         <v>202</v>
       </c>
-      <c r="B37" s="116"/>
-      <c r="C37" s="116"/>
-      <c r="D37" s="116"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="116"/>
+      <c r="B37" s="118"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
@@ -6635,15 +6632,15 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1">
-      <c r="A45" s="118" t="s">
-        <v>419</v>
-      </c>
-      <c r="B45" s="116"/>
-      <c r="C45" s="116"/>
-      <c r="D45" s="116"/>
-      <c r="E45" s="116"/>
-      <c r="F45" s="116"/>
-      <c r="G45" s="116"/>
+      <c r="A45" s="122" t="s">
+        <v>418</v>
+      </c>
+      <c r="B45" s="118"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
@@ -6651,12 +6648,12 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="30" customHeight="1">
-      <c r="A49" s="117" t="s">
+      <c r="A49" s="121" t="s">
         <v>205</v>
       </c>
-      <c r="B49" s="116"/>
-      <c r="C49" s="116"/>
-      <c r="D49" s="116"/>
+      <c r="B49" s="118"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="118"/>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
@@ -6683,12 +6680,12 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="30" customHeight="1">
-      <c r="A53" s="124" t="s">
-        <v>418</v>
-      </c>
-      <c r="B53" s="125"/>
-      <c r="C53" s="125"/>
-      <c r="D53" s="125"/>
+      <c r="A53" s="115" t="s">
+        <v>417</v>
+      </c>
+      <c r="B53" s="116"/>
+      <c r="C53" s="116"/>
+      <c r="D53" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7657,15 +7654,15 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A41" s="119" t="s">
-        <v>420</v>
-      </c>
-      <c r="B41" s="116"/>
-      <c r="C41" s="116"/>
-      <c r="D41" s="116"/>
-      <c r="E41" s="116"/>
-      <c r="F41" s="116"/>
-      <c r="G41" s="116"/>
+      <c r="A41" s="123" t="s">
+        <v>419</v>
+      </c>
+      <c r="B41" s="118"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
@@ -7894,15 +7891,15 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A64" s="120" t="s">
+      <c r="A64" s="124" t="s">
         <v>366</v>
       </c>
-      <c r="B64" s="116"/>
-      <c r="C64" s="116"/>
-      <c r="D64" s="116"/>
-      <c r="E64" s="116"/>
-      <c r="F64" s="116"/>
-      <c r="G64" s="116"/>
+      <c r="B64" s="118"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="118"/>
+      <c r="E64" s="118"/>
+      <c r="F64" s="118"/>
+      <c r="G64" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8051,13 +8048,11 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3" t="s">
-        <v>394</v>
-      </c>
+      <c r="A12" s="3"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="100" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B14" s="101"/>
       <c r="C14" s="101"/>
@@ -8071,19 +8066,19 @@
         <v>291</v>
       </c>
       <c r="B15" s="102" t="s">
+        <v>395</v>
+      </c>
+      <c r="C15" s="102" t="s">
         <v>396</v>
       </c>
-      <c r="C15" s="102" t="s">
+      <c r="D15" s="102" t="s">
         <v>397</v>
-      </c>
-      <c r="D15" s="102" t="s">
-        <v>398</v>
       </c>
       <c r="E15" s="102" t="s">
         <v>371</v>
       </c>
       <c r="F15" s="102" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -8188,7 +8183,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B21" s="106">
         <v>243275</v>
@@ -8208,7 +8203,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="100" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B23" s="101"/>
       <c r="C23" s="101"/>
@@ -8219,18 +8214,18 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="102" t="s">
+        <v>401</v>
+      </c>
+      <c r="C24" s="102" t="s">
         <v>402</v>
       </c>
-      <c r="C24" s="102" t="s">
-        <v>403</v>
-      </c>
       <c r="D24" s="102" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B25" s="49">
         <v>243275</v>
@@ -8244,7 +8239,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="109" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B26" s="49">
         <v>175970.42</v>
@@ -8258,18 +8253,18 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C28" s="110">
         <v>0.4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B30" s="106">
         <v>70388.168000000005</v>
@@ -8280,7 +8275,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="109" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B31" s="49">
         <v>44797.832000000002</v>
@@ -8294,7 +8289,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B32" s="104">
         <v>115186</v>
@@ -8308,7 +8303,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B34" s="47">
         <v>0.6110826662962513</v>
@@ -8322,7 +8317,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="100" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B36" s="101"/>
       <c r="C36" s="101"/>
@@ -8333,7 +8328,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="109" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B37" s="105">
         <v>0.77098412335436828</v>
@@ -8341,7 +8336,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="109" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B38" s="105">
         <v>0.68194919521469621</v>
@@ -8349,33 +8344,33 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B39" s="113">
         <v>-8.9034928139672065E-2</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="51.95" customHeight="1">
-      <c r="A40" s="121" t="s">
+      <c r="A40" s="125" t="s">
+        <v>415</v>
+      </c>
+      <c r="B40" s="118"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+    </row>
+    <row r="42" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A42" s="126" t="s">
         <v>416</v>
       </c>
-      <c r="B40" s="116"/>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-    </row>
-    <row r="42" spans="1:7" ht="80.099999999999994" customHeight="1">
-      <c r="A42" s="122" t="s">
-        <v>417</v>
-      </c>
-      <c r="B42" s="116"/>
-      <c r="C42" s="116"/>
-      <c r="D42" s="116"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="116"/>
+      <c r="B42" s="118"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="2">
